--- a/excelCfg/unit.xlsx
+++ b/excelCfg/unit.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit" sheetId="1" r:id="R751c6099fc2649ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit" sheetId="1" r:id="Rce8f447695484944"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1756,6 +1756,12 @@
       <x:c r="AP1" t="str">
         <x:v>可建造建筑</x:v>
       </x:c>
+      <x:c r="AQ1" t="str">
+        <x:v>模型路径</x:v>
+      </x:c>
+      <x:c r="AR1" t="str">
+        <x:v>模型缩放</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="3" t="s">
@@ -1884,6 +1890,12 @@
       <x:c r="AP2" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="AQ2" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="AR2" t="str">
+        <x:v>real</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="5" t="s">
@@ -2012,6 +2024,12 @@
       <x:c r="AP3" t="str">
         <x:v>Builds</x:v>
       </x:c>
+      <x:c r="AQ3" t="str">
+        <x:v>file</x:v>
+      </x:c>
+      <x:c r="AR3" t="str">
+        <x:v>modelScale</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="6" t="s">
@@ -2131,6 +2149,8 @@
       </x:c>
       <x:c r="AO4"/>
       <x:c r="AP4"/>
+      <x:c r="AQ4"/>
+      <x:c r="AR4"/>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="6" t="s">
@@ -2250,6 +2270,8 @@
       </x:c>
       <x:c r="AO5"/>
       <x:c r="AP5"/>
+      <x:c r="AQ5"/>
+      <x:c r="AR5"/>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="6" t="s">
@@ -2369,6 +2391,8 @@
       </x:c>
       <x:c r="AO6"/>
       <x:c r="AP6"/>
+      <x:c r="AQ6"/>
+      <x:c r="AR6"/>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="6" t="s">
@@ -2488,6 +2512,12 @@
       </x:c>
       <x:c r="AO7"/>
       <x:c r="AP7"/>
+      <x:c r="AQ7" t="str">
+        <x:v>models\arthas_v2\Arthas_v2</x:v>
+      </x:c>
+      <x:c r="AR7" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="6" t="s">
@@ -2571,6 +2601,8 @@
       <x:c r="AN8" s="8"/>
       <x:c r="AO8"/>
       <x:c r="AP8"/>
+      <x:c r="AQ8"/>
+      <x:c r="AR8"/>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="6" t="s">
@@ -2654,6 +2686,8 @@
       <x:c r="AN9" s="8"/>
       <x:c r="AO9"/>
       <x:c r="AP9"/>
+      <x:c r="AQ9"/>
+      <x:c r="AR9"/>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="6" t="s">
@@ -2737,6 +2771,8 @@
       <x:c r="AN10" s="8"/>
       <x:c r="AO10"/>
       <x:c r="AP10"/>
+      <x:c r="AQ10"/>
+      <x:c r="AR10"/>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="6" t="s">
@@ -2825,6 +2861,8 @@
       <x:c r="AN11" s="8"/>
       <x:c r="AO11"/>
       <x:c r="AP11"/>
+      <x:c r="AQ11"/>
+      <x:c r="AR11"/>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="6" t="s">
@@ -2908,6 +2946,8 @@
       <x:c r="AN12" s="8"/>
       <x:c r="AO12"/>
       <x:c r="AP12"/>
+      <x:c r="AQ12"/>
+      <x:c r="AR12"/>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="6" t="s">
@@ -2991,6 +3031,8 @@
       <x:c r="AN13" s="8"/>
       <x:c r="AO13"/>
       <x:c r="AP13"/>
+      <x:c r="AQ13"/>
+      <x:c r="AR13"/>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="6" t="s">
@@ -3074,6 +3116,8 @@
       <x:c r="AN14" s="8"/>
       <x:c r="AO14"/>
       <x:c r="AP14"/>
+      <x:c r="AQ14"/>
+      <x:c r="AR14"/>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="6" t="s">
@@ -3162,6 +3206,8 @@
       <x:c r="AN15" s="8"/>
       <x:c r="AO15"/>
       <x:c r="AP15"/>
+      <x:c r="AQ15"/>
+      <x:c r="AR15"/>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="6" t="s">
@@ -3245,6 +3291,8 @@
       <x:c r="AN16" s="8"/>
       <x:c r="AO16"/>
       <x:c r="AP16"/>
+      <x:c r="AQ16"/>
+      <x:c r="AR16"/>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="6" t="s">
@@ -3328,6 +3376,8 @@
       <x:c r="AN17" s="8"/>
       <x:c r="AO17"/>
       <x:c r="AP17"/>
+      <x:c r="AQ17"/>
+      <x:c r="AR17"/>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="6" t="s">
@@ -3411,6 +3461,8 @@
       <x:c r="AN18" s="8"/>
       <x:c r="AO18"/>
       <x:c r="AP18"/>
+      <x:c r="AQ18"/>
+      <x:c r="AR18"/>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="6" t="s">
@@ -3499,6 +3551,8 @@
       <x:c r="AN19" s="8"/>
       <x:c r="AO19"/>
       <x:c r="AP19"/>
+      <x:c r="AQ19"/>
+      <x:c r="AR19"/>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="6" t="s">
@@ -3582,6 +3636,8 @@
       <x:c r="AN20" s="8"/>
       <x:c r="AO20"/>
       <x:c r="AP20"/>
+      <x:c r="AQ20"/>
+      <x:c r="AR20"/>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="6" t="s">
@@ -3665,6 +3721,8 @@
       <x:c r="AN21" s="8"/>
       <x:c r="AO21"/>
       <x:c r="AP21"/>
+      <x:c r="AQ21"/>
+      <x:c r="AR21"/>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="6" t="s">
@@ -3748,6 +3806,8 @@
       <x:c r="AN22" s="8"/>
       <x:c r="AO22"/>
       <x:c r="AP22"/>
+      <x:c r="AQ22"/>
+      <x:c r="AR22"/>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="6" t="s">
@@ -3836,6 +3896,8 @@
       <x:c r="AN23" s="8"/>
       <x:c r="AO23"/>
       <x:c r="AP23"/>
+      <x:c r="AQ23"/>
+      <x:c r="AR23"/>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="6" t="s">
@@ -3919,6 +3981,8 @@
       <x:c r="AN24" s="8"/>
       <x:c r="AO24"/>
       <x:c r="AP24"/>
+      <x:c r="AQ24"/>
+      <x:c r="AR24"/>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="6" t="s">
@@ -4002,6 +4066,8 @@
       <x:c r="AN25" s="8"/>
       <x:c r="AO25"/>
       <x:c r="AP25"/>
+      <x:c r="AQ25"/>
+      <x:c r="AR25"/>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="6" t="s">
@@ -4085,6 +4151,8 @@
       <x:c r="AN26" s="8"/>
       <x:c r="AO26"/>
       <x:c r="AP26"/>
+      <x:c r="AQ26"/>
+      <x:c r="AR26"/>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="6" t="s">
@@ -4173,6 +4241,8 @@
       <x:c r="AN27" s="8"/>
       <x:c r="AO27"/>
       <x:c r="AP27"/>
+      <x:c r="AQ27"/>
+      <x:c r="AR27"/>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="6" t="s">
@@ -4256,6 +4326,8 @@
       <x:c r="AN28" s="8"/>
       <x:c r="AO28"/>
       <x:c r="AP28"/>
+      <x:c r="AQ28"/>
+      <x:c r="AR28"/>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="6" t="s">
@@ -4339,6 +4411,8 @@
       <x:c r="AN29" s="8"/>
       <x:c r="AO29"/>
       <x:c r="AP29"/>
+      <x:c r="AQ29"/>
+      <x:c r="AR29"/>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
       <x:c r="A30" s="6" t="s">
@@ -4422,6 +4496,8 @@
       <x:c r="AN30" s="8"/>
       <x:c r="AO30"/>
       <x:c r="AP30"/>
+      <x:c r="AQ30"/>
+      <x:c r="AR30"/>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
       <x:c r="A31" s="6" t="s">
@@ -4510,6 +4586,8 @@
       <x:c r="AN31" s="8"/>
       <x:c r="AO31"/>
       <x:c r="AP31"/>
+      <x:c r="AQ31"/>
+      <x:c r="AR31"/>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
       <x:c r="A32" s="6" t="s">
@@ -4593,6 +4671,8 @@
       <x:c r="AN32" s="8"/>
       <x:c r="AO32"/>
       <x:c r="AP32"/>
+      <x:c r="AQ32"/>
+      <x:c r="AR32"/>
     </x:row>
     <x:row r="33" ht="24" customHeight="1">
       <x:c r="A33" s="6" t="s">
@@ -4676,6 +4756,8 @@
       <x:c r="AN33" s="8"/>
       <x:c r="AO33"/>
       <x:c r="AP33"/>
+      <x:c r="AQ33"/>
+      <x:c r="AR33"/>
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
       <x:c r="A34" s="6" t="s">
@@ -4759,6 +4841,8 @@
       <x:c r="AN34" s="8"/>
       <x:c r="AO34"/>
       <x:c r="AP34"/>
+      <x:c r="AQ34"/>
+      <x:c r="AR34"/>
     </x:row>
     <x:row r="35" ht="24" customHeight="1">
       <x:c r="A35" s="6" t="s">
@@ -4847,6 +4931,8 @@
       <x:c r="AN35" s="8"/>
       <x:c r="AO35"/>
       <x:c r="AP35"/>
+      <x:c r="AQ35"/>
+      <x:c r="AR35"/>
     </x:row>
     <x:row r="36" ht="24" customHeight="1">
       <x:c r="A36" s="6" t="s">
@@ -4930,6 +5016,8 @@
       <x:c r="AN36" s="8"/>
       <x:c r="AO36"/>
       <x:c r="AP36"/>
+      <x:c r="AQ36"/>
+      <x:c r="AR36"/>
     </x:row>
     <x:row r="37" ht="24" customHeight="1">
       <x:c r="A37" s="6" t="s">
@@ -5013,6 +5101,8 @@
       <x:c r="AN37" s="8"/>
       <x:c r="AO37"/>
       <x:c r="AP37"/>
+      <x:c r="AQ37"/>
+      <x:c r="AR37"/>
     </x:row>
     <x:row r="38" ht="24" customHeight="1">
       <x:c r="A38" s="6" t="s">
@@ -5096,6 +5186,8 @@
       <x:c r="AN38" s="8"/>
       <x:c r="AO38"/>
       <x:c r="AP38"/>
+      <x:c r="AQ38"/>
+      <x:c r="AR38"/>
     </x:row>
     <x:row r="39" ht="24" customHeight="1">
       <x:c r="A39" s="6" t="s">
@@ -5184,6 +5276,8 @@
       <x:c r="AN39" s="8"/>
       <x:c r="AO39"/>
       <x:c r="AP39"/>
+      <x:c r="AQ39"/>
+      <x:c r="AR39"/>
     </x:row>
     <x:row r="40" ht="24" customHeight="1">
       <x:c r="A40" s="6" t="s">
@@ -5267,6 +5361,8 @@
       <x:c r="AN40" s="8"/>
       <x:c r="AO40"/>
       <x:c r="AP40"/>
+      <x:c r="AQ40"/>
+      <x:c r="AR40"/>
     </x:row>
     <x:row r="41" ht="24" customHeight="1">
       <x:c r="A41" s="6" t="s">
@@ -5350,6 +5446,8 @@
       <x:c r="AN41" s="8"/>
       <x:c r="AO41"/>
       <x:c r="AP41"/>
+      <x:c r="AQ41"/>
+      <x:c r="AR41"/>
     </x:row>
     <x:row r="42" ht="24" customHeight="1">
       <x:c r="A42" s="6" t="s">
@@ -5433,6 +5531,8 @@
       <x:c r="AN42" s="8"/>
       <x:c r="AO42"/>
       <x:c r="AP42"/>
+      <x:c r="AQ42"/>
+      <x:c r="AR42"/>
     </x:row>
     <x:row r="43" ht="24" customHeight="1">
       <x:c r="A43" s="6" t="s">
@@ -5521,6 +5621,8 @@
       <x:c r="AN43" s="8"/>
       <x:c r="AO43"/>
       <x:c r="AP43"/>
+      <x:c r="AQ43"/>
+      <x:c r="AR43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="s">
@@ -5552,6 +5654,8 @@
       <x:c r="AN44" s="8"/>
       <x:c r="AO44"/>
       <x:c r="AP44"/>
+      <x:c r="AQ44"/>
+      <x:c r="AR44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
@@ -5664,6 +5768,8 @@
       <x:c r="AP45" t="str">
         <x:v>""</x:v>
       </x:c>
+      <x:c r="AQ45"/>
+      <x:c r="AR45"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excelCfg/unit.xlsx
+++ b/excelCfg/unit.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit" sheetId="1" r:id="Rce8f447695484944"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit" sheetId="1" r:id="Raa1fd8ffba2d41ca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5771,6 +5771,190 @@
       <x:c r="AQ45"/>
       <x:c r="AR45"/>
     </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>G0M1</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>ninf</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>金币恶魔</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>金币怪</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>携带大量金币的恶魔。</x:v>
+      </x:c>
+      <x:c r="F46"/>
+      <x:c r="G46"/>
+      <x:c r="H46"/>
+      <x:c r="I46"/>
+      <x:c r="J46"/>
+      <x:c r="K46"/>
+      <x:c r="L46"/>
+      <x:c r="M46" t="n">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="N46"/>
+      <x:c r="O46"/>
+      <x:c r="P46" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q46" t="n">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="R46" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="S46"/>
+      <x:c r="T46"/>
+      <x:c r="U46" t="str">
+        <x:v>""</x:v>
+      </x:c>
+      <x:c r="V46"/>
+      <x:c r="W46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X46"/>
+      <x:c r="Y46" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="Z46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA46" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="AB46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC46"/>
+      <x:c r="AD46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI46" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AJ46" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="AK46" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="AL46"/>
+      <x:c r="AM46"/>
+      <x:c r="AN46"/>
+      <x:c r="AO46"/>
+      <x:c r="AP46"/>
+      <x:c r="AQ46"/>
+      <x:c r="AR46"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>X0M1</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>nbdo</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>经验恶魔</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>经验怪</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>携带大量经验的恶魔。</x:v>
+      </x:c>
+      <x:c r="F47"/>
+      <x:c r="G47"/>
+      <x:c r="H47"/>
+      <x:c r="I47"/>
+      <x:c r="J47"/>
+      <x:c r="K47"/>
+      <x:c r="L47"/>
+      <x:c r="M47" t="n">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="N47"/>
+      <x:c r="O47"/>
+      <x:c r="P47" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q47" t="n">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="R47" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="S47"/>
+      <x:c r="T47"/>
+      <x:c r="U47" t="str">
+        <x:v>""</x:v>
+      </x:c>
+      <x:c r="V47"/>
+      <x:c r="W47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X47"/>
+      <x:c r="Y47" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="Z47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB47" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="AC47"/>
+      <x:c r="AD47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI47" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AJ47" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="AK47" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="AL47"/>
+      <x:c r="AM47"/>
+      <x:c r="AN47"/>
+      <x:c r="AO47"/>
+      <x:c r="AP47"/>
+      <x:c r="AQ47"/>
+      <x:c r="AR47"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
